--- a/fixtures/xlsx/booleans/input.xlsx
+++ b/fixtures/xlsx/booleans/input.xlsx
@@ -10,16 +10,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Label</t>
+    <t>True</t>
   </si>
   <si>
-    <t>True</t>
+    <t>Value</t>
   </si>
   <si>
     <t>False</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>Label</t>
   </si>
 </sst>
 </file>
@@ -29,15 +29,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>

--- a/fixtures/xlsx/booleans/input.xlsx
+++ b/fixtures/xlsx/booleans/input.xlsx
@@ -10,16 +10,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
     <t>True</t>
   </si>
   <si>
     <t>Value</t>
-  </si>
-  <si>
-    <t>False</t>
-  </si>
-  <si>
-    <t>Label</t>
   </si>
 </sst>
 </file>
@@ -29,15 +29,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -45,7 +45,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="b">
         <v>0</v>
